--- a/outputs/evaluation/decision/v2/CF_M05/CF_M05_decision_eval_avg.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M05/CF_M05_decision_eval_avg.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6746</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3333</v>
+        <v>0.3077</v>
       </c>
       <c r="D2" t="n">
-        <v>0.891</v>
+        <v>0.8882</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1472</v>
+        <v>0.3333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6945</v>
+        <v>0.6222</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9482</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6945</v>
+        <v>0.5889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3333</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3333</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.666700000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6746</v>
+        <v>0.5741000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3333</v>
+        <v>0.3077</v>
       </c>
     </row>
     <row r="9">
